--- a/eda/ket_qua/ket_qua_modelSVM_processed.xlsx
+++ b/eda/ket_qua/ket_qua_modelSVM_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,58 @@
       </c>
       <c r="H2" t="n">
         <v>0.5899280575539568</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7655136268343815</v>
+      </c>
+      <c r="D3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5899280575539568</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7530864197530864</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7316017316017316</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7485674353598881</v>
+      </c>
+      <c r="D4" t="n">
+        <v>57</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>112</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6477272727272727</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modelSVM_processed.xlsx
+++ b/eda/ket_qua/ket_qua_modelSVM_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,54 +498,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7839506172839507</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7532467532467533</v>
+        <v>0.7445887445887446</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7655136268343815</v>
+        <v>0.7618448637316562</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5899280575539568</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.7530864197530864</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7316017316017316</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7485674353598881</v>
-      </c>
-      <c r="D4" t="n">
-        <v>57</v>
-      </c>
-      <c r="E4" t="n">
-        <v>38</v>
-      </c>
-      <c r="F4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G4" t="n">
-        <v>112</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.562962962962963</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modelSVM_processed.xlsx
+++ b/eda/ket_qua/ket_qua_modelSVM_processed.xlsx
@@ -498,28 +498,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7098765432098766</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7445887445887446</v>
+        <v>0.7229437229437229</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7618448637316562</v>
+        <v>0.729979035639413</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="H3" t="n">
-        <v>0.562962962962963</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
   </sheetData>
